--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N18_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0001T0006Z000C1N18_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.7492083524376</v>
+        <v>5.159246357271111</v>
       </c>
       <c r="D2" t="n">
-        <v>31.72824542068405</v>
+        <v>5.155839880861159</v>
       </c>
       <c r="E2" t="n">
-        <v>11.01521461408156</v>
+        <v>1.789972374788254</v>
       </c>
       <c r="F2" t="n">
-        <v>19.5709377626996</v>
+        <v>3.180277386438686</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.12942904615816</v>
+        <v>2.458532220000702</v>
       </c>
       <c r="D3" t="n">
-        <v>15.00424855103073</v>
+        <v>2.438190389542493</v>
       </c>
       <c r="E3" t="n">
-        <v>11.01521461408156</v>
+        <v>1.789972374788254</v>
       </c>
       <c r="F3" t="n">
-        <v>19.5709377626996</v>
+        <v>3.180277386438686</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>42.28220584360089</v>
+        <v>6.870858449585145</v>
       </c>
       <c r="D4" t="n">
-        <v>64.84192862559773</v>
+        <v>10.53681340165963</v>
       </c>
       <c r="E4" t="n">
-        <v>11.01521461408156</v>
+        <v>1.789972374788254</v>
       </c>
       <c r="F4" t="n">
-        <v>19.5709377626996</v>
+        <v>3.180277386438686</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>17.58062983585552</v>
+        <v>2.856852348326522</v>
       </c>
       <c r="D5" t="n">
-        <v>19.10210571886651</v>
+        <v>3.104092179315808</v>
       </c>
       <c r="E5" t="n">
-        <v>11.01521461408156</v>
+        <v>1.789972374788254</v>
       </c>
       <c r="F5" t="n">
-        <v>19.5709377626996</v>
+        <v>3.180277386438686</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
